--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T11:44:16+00:00</t>
+    <t>2026-07-15T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T12:32:02+00:00</t>
+    <t>2026-07-15T14:55:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-15T14:55:56+00:00</t>
+    <t>2026-07-16T09:23:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T09:23:28+00:00</t>
+    <t>2026-07-17T06:35:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T06:35:14+00:00</t>
+    <t>2026-07-20T14:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-20T14:28:37+00:00</t>
+    <t>2026-07-21T08:19:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:19:16+00:00</t>
+    <t>2026-07-21T08:48:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:48:20+00:00</t>
+    <t>2026-07-21T09:53:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T09:53:07+00:00</t>
+    <t>2026-07-21T13:00:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T13:00:05+00:00</t>
+    <t>2026-07-27T06:31:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T06:31:56+00:00</t>
+    <t>2026-07-27T07:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:32:14+00:00</t>
+    <t>2026-07-27T07:43:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T07:43:34+00:00</t>
+    <t>2026-07-27T08:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T08:58:26+00:00</t>
+    <t>2026-07-27T09:29:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T09:29:06+00:00</t>
+    <t>2026-07-27T09:54:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T09:54:42+00:00</t>
+    <t>2026-07-27T10:14:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:14:55+00:00</t>
+    <t>2026-07-27T10:27:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:27:19+00:00</t>
+    <t>2026-07-27T10:49:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T10:49:55+00:00</t>
+    <t>2026-07-28T05:51:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T05:51:13+00:00</t>
+    <t>2026-07-28T06:19:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T06:19:15+00:00</t>
+    <t>2026-07-28T06:47:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T06:47:20+00:00</t>
+    <t>2026-07-28T13:00:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T13:00:26+00:00</t>
+    <t>2026-07-28T13:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T13:42:50+00:00</t>
+    <t>2026-07-28T14:03:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T14:03:46+00:00</t>
+    <t>2026-07-29T06:44:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T06:44:02+00:00</t>
+    <t>2026-07-29T11:08:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:08:45+00:00</t>
+    <t>2026-07-29T11:32:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:32:55+00:00</t>
+    <t>2026-07-29T11:56:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T11:56:42+00:00</t>
+    <t>2026-07-30T06:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T06:46:32+00:00</t>
+    <t>2026-07-30T07:01:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:01:31+00:00</t>
+    <t>2026-07-30T10:22:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:22:13+00:00</t>
+    <t>2026-07-31T07:01:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T07:01:03+00:00</t>
+    <t>2026-07-31T08:34:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T08:34:12+00:00</t>
+    <t>2026-07-31T10:47:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T10:47:24+00:00</t>
+    <t>2026-07-31T12:19:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T12:19:34+00:00</t>
+    <t>2026-08-03T09:14:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T09:14:34+00:00</t>
+    <t>2026-08-03T10:33:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T10:33:06+00:00</t>
+    <t>2026-08-06T10:46:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T10:46:09+00:00</t>
+    <t>2026-08-07T07:27:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-07T07:27:35+00:00</t>
+    <t>2026-08-10T07:07:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T07:07:45+00:00</t>
+    <t>2026-08-10T09:07:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T09:07:49+00:00</t>
+    <t>2026-08-10T10:07:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-10T10:07:23+00:00</t>
+    <t>2026-08-12T14:05:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T14:05:51+00:00</t>
+    <t>2026-08-12T15:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T15:02:16+00:00</t>
+    <t>2026-08-13T10:03:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-13T10:03:40+00:00</t>
+    <t>2026-08-14T12:06:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-14T12:06:36+00:00</t>
+    <t>2026-08-20T12:53:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:53:18+00:00</t>
+    <t>2026-08-26T13:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T13:50:30+00:00</t>
+    <t>2026-08-28T05:58:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T05:58:13+00:00</t>
+    <t>2026-08-28T07:25:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T07:25:52+00:00</t>
+    <t>2026-08-28T08:10:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T08:10:45+00:00</t>
+    <t>2026-08-28T11:38:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T11:38:22+00:00</t>
+    <t>2026-08-28T12:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T12:52:33+00:00</t>
+    <t>2026-08-31T10:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:02:50+00:00</t>
+    <t>2026-09-01T06:51:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T06:51:10+00:00</t>
+    <t>2026-09-01T11:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T11:42:45+00:00</t>
+    <t>2026-09-01T12:48:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T12:48:31+00:00</t>
+    <t>2026-09-01T13:57:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T13:57:21+00:00</t>
+    <t>2026-09-03T13:31:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-03T13:31:10+00:00</t>
+    <t>2026-09-07T04:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T04:47:29+00:00</t>
+    <t>2026-09-07T06:52:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T06:52:33+00:00</t>
+    <t>2026-09-07T07:43:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:43:01+00:00</t>
+    <t>2026-09-07T07:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T07:56:25+00:00</t>
+    <t>2026-09-07T09:23:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T09:23:06+00:00</t>
+    <t>2026-09-07T10:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:17:45+00:00</t>
+    <t>2026-09-07T10:50:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:50:55+00:00</t>
+    <t>2026-09-08T06:03:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:03:03+00:00</t>
+    <t>2026-09-08T06:16:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:16:43+00:00</t>
+    <t>2026-09-08T06:28:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:28:20+00:00</t>
+    <t>2026-09-08T06:46:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:46:13+00:00</t>
+    <t>2026-09-08T10:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:19:13+00:00</t>
+    <t>2026-09-08T10:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T10:46:31+00:00</t>
+    <t>2026-09-08T11:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T11:50:41+00:00</t>
+    <t>2026-09-08T12:56:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T12:56:54+00:00</t>
+    <t>2026-09-09T04:29:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T04:29:28+00:00</t>
+    <t>2026-09-09T07:41:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T07:41:46+00:00</t>
+    <t>2026-09-09T08:03:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T08:03:40+00:00</t>
+    <t>2026-09-09T09:18:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T09:18:29+00:00</t>
+    <t>2026-09-09T14:48:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T14:48:33+00:00</t>
+    <t>2026-09-10T08:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T08:40:11+00:00</t>
+    <t>2026-09-10T09:01:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:01:10+00:00</t>
+    <t>2026-09-10T09:35:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:35:03+00:00</t>
+    <t>2026-09-10T09:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T09:50:09+00:00</t>
+    <t>2026-09-10T10:02:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:02:23+00:00</t>
+    <t>2026-09-10T11:15:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:15:10+00:00</t>
+    <t>2026-09-10T11:24:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:24:50+00:00</t>
+    <t>2026-09-10T11:47:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T11:47:23+00:00</t>
+    <t>2026-09-10T14:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T14:22:40+00:00</t>
+    <t>2026-09-11T07:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
+++ b/r4-ELGA-e-Diagnose-main/StructureDefinition-at-elga-ediag-reported.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T07:57:50+00:00</t>
+    <t>2026-09-11T08:25:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
